--- a/24_DS_CLUB_BATCH1_AHM/Attendance_new.xlsx
+++ b/24_DS_CLUB_BATCH1_AHM/Attendance_new.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_CLUB_BATCH1_AHM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C54E80-EE61-43D5-94B0-3ADB09CE28BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A5CFB2-07C0-489C-B354-7813A9B954E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{1FF622FD-D8C9-422F-8436-9CCD6703699A}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="27">
   <si>
     <t>Adwait Kathiriya</t>
   </si>
@@ -100,6 +100,12 @@
   </si>
   <si>
     <t>Diya Chaudhary</t>
+  </si>
+  <si>
+    <t>Vrund Patel</t>
+  </si>
+  <si>
+    <t>Ivanshi Thakkar</t>
   </si>
 </sst>
 </file>
@@ -452,13 +458,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D461A628-08A5-4F1C-BDF6-E1294AEC5259}">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -468,8 +474,11 @@
       <c r="C1" s="1">
         <v>45746</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" s="1">
+        <v>45753</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -479,8 +488,11 @@
       <c r="C2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -491,7 +503,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -501,8 +513,11 @@
       <c r="C4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -512,8 +527,11 @@
       <c r="C5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -523,8 +541,11 @@
       <c r="C6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -534,8 +555,11 @@
       <c r="C7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -545,8 +569,11 @@
       <c r="C8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -556,8 +583,11 @@
       <c r="C9" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -567,8 +597,11 @@
       <c r="C10" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -578,8 +611,11 @@
       <c r="C11" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -589,8 +625,11 @@
       <c r="C12" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -600,8 +639,11 @@
       <c r="C13" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -611,8 +653,11 @@
       <c r="C14" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -622,8 +667,11 @@
       <c r="C15" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -633,8 +681,11 @@
       <c r="C16" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -644,8 +695,11 @@
       <c r="C17" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -655,8 +709,11 @@
       <c r="C18" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -666,8 +723,11 @@
       <c r="C19" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -677,8 +737,11 @@
       <c r="C20" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -688,8 +751,11 @@
       <c r="C21" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -697,6 +763,25 @@
         <v>22</v>
       </c>
       <c r="C22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" t="s">
         <v>22</v>
       </c>
     </row>

--- a/24_DS_CLUB_BATCH1_AHM/Attendance_new.xlsx
+++ b/24_DS_CLUB_BATCH1_AHM/Attendance_new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_CLUB_BATCH1_AHM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A5CFB2-07C0-489C-B354-7813A9B954E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9B6B06C-8663-496C-BDF6-D7B38BE25339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{1FF622FD-D8C9-422F-8436-9CCD6703699A}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="26">
   <si>
     <t>Adwait Kathiriya</t>
   </si>
@@ -103,9 +103,6 @@
   </si>
   <si>
     <t>Vrund Patel</t>
-  </si>
-  <si>
-    <t>Ivanshi Thakkar</t>
   </si>
 </sst>
 </file>
@@ -458,13 +455,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D461A628-08A5-4F1C-BDF6-E1294AEC5259}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -477,8 +474,11 @@
       <c r="D1" s="1">
         <v>45753</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" s="1">
+        <v>45760</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -491,8 +491,11 @@
       <c r="D2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -502,8 +505,14 @@
       <c r="C3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -516,8 +525,11 @@
       <c r="D4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -530,8 +542,11 @@
       <c r="D5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -544,8 +559,11 @@
       <c r="D6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -558,8 +576,11 @@
       <c r="D7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -572,8 +593,11 @@
       <c r="D8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -586,8 +610,11 @@
       <c r="D9" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -600,8 +627,11 @@
       <c r="D10" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -614,8 +644,11 @@
       <c r="D11" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -628,8 +661,11 @@
       <c r="D12" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -642,8 +678,11 @@
       <c r="D13" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -656,8 +695,11 @@
       <c r="D14" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -670,8 +712,11 @@
       <c r="D15" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -684,8 +729,11 @@
       <c r="D16" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -698,8 +746,11 @@
       <c r="D17" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -712,8 +763,11 @@
       <c r="D18" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -726,8 +780,11 @@
       <c r="D19" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -740,8 +797,11 @@
       <c r="D20" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -754,8 +814,11 @@
       <c r="D21" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -768,21 +831,19 @@
       <c r="D22" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>25</v>
       </c>
       <c r="D23" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24" t="s">
-        <v>22</v>
+      <c r="E23" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
